--- a/District_GIS_Parakh_CMMI_L5_Artifacts/District GIS Parakh Artefacts/Katni/DMF Mining releted for DMF alloction before surveys/Panchayat and urban.xlsx
+++ b/District_GIS_Parakh_CMMI_L5_Artifacts/District GIS Parakh Artefacts/Katni/DMF Mining releted for DMF alloction before surveys/Panchayat and urban.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Department_Katni\Mining+DMF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Organization_Docs\District_GIS_Parakh_CMMI_L5_Artifacts\District GIS Parakh Artefacts\Katni\DMF Mining releted for DMF alloction before surveys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6865189-3AC8-4B30-B6EE-8C105DA93BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BFAF27-3B92-484A-8F15-E1356C80DC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
